--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,18 +31,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B91C1C"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -55,14 +45,8 @@
         <bgColor rgb="001E293B"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -70,31 +54,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E2E8F0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,13 +428,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -509,251 +477,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC_SEL_AUTH_010</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Selenium Web</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Verify Authentication scenario 10: detailed validation of interface controls, security constraints, and layout formatting.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC_SEL_FORM_008</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Selenium Web</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Verify Forms scenario 8: detailed validation of interface controls, security constraints, and layout formatting.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC_SEL_FILE_002</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Selenium Web</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Verify File Upload scenario 2: detailed validation of interface controls, security constraints, and layout formatting.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC_SEC_INJ_002</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Backend Security</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Injection Tests</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Vulnerability audit check 2 for Injection Tests: analysis of security controls, code structures, and parameters.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC_SEC_INJ_010</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Backend Security</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Injection Tests</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Vulnerability audit check 10 for Injection Tests: analysis of security controls, code structures, and parameters.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC_SEC_CONFIG_001</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Backend Security</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Configuration Tests</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Vulnerability audit check 1 for Configuration Tests: analysis of security controls, code structures, and parameters.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC_SEC_CONFIG_005</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Backend Security</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Configuration Tests</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Vulnerability audit check 5 for Configuration Tests: analysis of security controls, code structures, and parameters.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
